--- a/centralized/experiment_results/E1/results.xlsx
+++ b/centralized/experiment_results/E1/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>grid_size</t>
   </si>
@@ -27,6 +27,12 @@
   </si>
   <si>
     <t>n_failures</t>
+  </si>
+  <si>
+    <t>num_experiments</t>
+  </si>
+  <si>
+    <t>experiment_id</t>
   </si>
   <si>
     <t>n_targets_found</t>
@@ -44,7 +50,7 @@
     <t>mean_found</t>
   </si>
   <si>
-    <t>runs</t>
+    <t>total_runs</t>
   </si>
   <si>
     <t>avg_n_targets_found</t>
@@ -66,16 +72,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -91,7 +89,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -99,30 +97,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -425,42 +405,50 @@
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>50</v>
       </c>
@@ -468,7 +456,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -477,277 +465,3487 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>241</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>380</v>
+        <v>15</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="I2">
-        <v>0.6655263157894744</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>349</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>0.5025787965616051</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>348</v>
+      </c>
+      <c r="I3">
+        <v>353</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>0.465722379603399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>15</v>
+      </c>
+      <c r="H4">
+        <v>268</v>
+      </c>
+      <c r="I4">
+        <v>340</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>0.6211764705882362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>281</v>
+      </c>
+      <c r="I5">
+        <v>350</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>0.5984761904761908</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>50</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>338</v>
+      </c>
+      <c r="I6">
+        <v>347</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>0.6384245917387128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>50</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>359</v>
+      </c>
+      <c r="I7">
+        <v>364</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>0.5126373626373626</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>50</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>309</v>
+      </c>
+      <c r="I8">
+        <v>323</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>0.4078431372549017</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>50</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>291</v>
+      </c>
+      <c r="I9">
+        <v>349</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>0.5134670487106014</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>50</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>15</v>
+      </c>
+      <c r="H10">
+        <v>303</v>
+      </c>
+      <c r="I10">
+        <v>338</v>
+      </c>
+      <c r="J10">
+        <v>100</v>
+      </c>
+      <c r="K10">
+        <v>0.5706114398422092</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>15</v>
+      </c>
+      <c r="H11">
+        <v>312</v>
+      </c>
+      <c r="I11">
+        <v>362</v>
+      </c>
+      <c r="J11">
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>0.6631675874769809</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>100</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>569</v>
+      </c>
+      <c r="I12">
+        <v>644</v>
+      </c>
+      <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
+        <v>0.5076086956521748</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>100</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>30</v>
+      </c>
+      <c r="H13">
+        <v>649</v>
+      </c>
+      <c r="I13">
+        <v>692</v>
+      </c>
+      <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>0.4991811175337158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>100</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>30</v>
+      </c>
+      <c r="H14">
+        <v>619</v>
+      </c>
+      <c r="I14">
+        <v>736</v>
+      </c>
+      <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
+        <v>0.5851902173913036</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>100</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>615</v>
+      </c>
+      <c r="I15">
+        <v>680</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>0.6004901960784291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>100</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>675</v>
+      </c>
+      <c r="I16">
+        <v>723</v>
+      </c>
+      <c r="J16">
+        <v>100</v>
+      </c>
+      <c r="K16">
+        <v>0.6266482249884688</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>100</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17">
+        <v>30</v>
+      </c>
+      <c r="H17">
+        <v>628</v>
+      </c>
+      <c r="I17">
+        <v>692</v>
+      </c>
+      <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
+        <v>0.6836223506743703</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>100</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
+        <v>30</v>
+      </c>
+      <c r="H18">
+        <v>636</v>
+      </c>
+      <c r="I18">
+        <v>654</v>
+      </c>
+      <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
+        <v>0.4176860346585118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>100</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>30</v>
+      </c>
+      <c r="H19">
+        <v>597</v>
+      </c>
+      <c r="I19">
+        <v>659</v>
+      </c>
+      <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>0.5175518462316648</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>100</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>30</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>30</v>
+      </c>
+      <c r="H20">
+        <v>655</v>
+      </c>
+      <c r="I20">
+        <v>708</v>
+      </c>
+      <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>0.616101694915252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>100</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>636</v>
+      </c>
+      <c r="I21">
+        <v>666</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
+        <v>0.5892392392392347</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22">
+        <v>150</v>
+      </c>
+      <c r="B22">
+        <v>15</v>
+      </c>
+      <c r="C22">
+        <v>45</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>45</v>
+      </c>
+      <c r="H22">
+        <v>971</v>
+      </c>
+      <c r="I22">
+        <v>1064</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
+        <v>0.6097953216374278</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23">
+        <v>150</v>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>45</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>45</v>
+      </c>
+      <c r="H23">
+        <v>686</v>
+      </c>
+      <c r="I23">
+        <v>1120</v>
+      </c>
+      <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>0.6826785714285718</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24">
+        <v>150</v>
+      </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
+      <c r="C24">
+        <v>45</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>45</v>
+      </c>
+      <c r="H24">
+        <v>1051</v>
+      </c>
+      <c r="I24">
+        <v>1119</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <v>0.6339787508688277</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25">
+        <v>150</v>
+      </c>
+      <c r="B25">
+        <v>15</v>
+      </c>
+      <c r="C25">
+        <v>45</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <v>45</v>
+      </c>
+      <c r="H25">
+        <v>998</v>
+      </c>
+      <c r="I25">
+        <v>1162</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>0.630770701855038</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26">
+        <v>150</v>
+      </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
+      <c r="C26">
+        <v>45</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>45</v>
+      </c>
+      <c r="H26">
+        <v>782</v>
+      </c>
+      <c r="I26">
+        <v>1000</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>0.7051333333333329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27">
+        <v>150</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>45</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27">
+        <v>45</v>
+      </c>
+      <c r="H27">
+        <v>994</v>
+      </c>
+      <c r="I27">
+        <v>1037</v>
+      </c>
+      <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
+        <v>0.6342655094824771</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28">
+        <v>150</v>
+      </c>
+      <c r="B28">
+        <v>15</v>
+      </c>
+      <c r="C28">
+        <v>45</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <v>45</v>
+      </c>
+      <c r="H28">
+        <v>888</v>
+      </c>
+      <c r="I28">
+        <v>1030</v>
+      </c>
+      <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
+        <v>0.5933764832793952</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29">
+        <v>150</v>
+      </c>
+      <c r="B29">
+        <v>15</v>
+      </c>
+      <c r="C29">
+        <v>45</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="G29">
+        <v>45</v>
+      </c>
+      <c r="H29">
+        <v>922</v>
+      </c>
+      <c r="I29">
+        <v>1183</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>0.6393350239504094</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30">
+        <v>150</v>
+      </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
+      <c r="C30">
+        <v>45</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>9</v>
+      </c>
+      <c r="G30">
+        <v>45</v>
+      </c>
+      <c r="H30">
+        <v>940</v>
+      </c>
+      <c r="I30">
+        <v>976</v>
+      </c>
+      <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
+        <v>0.5812158469945338</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31">
+        <v>150</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31">
+        <v>45</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>45</v>
+      </c>
+      <c r="H31">
+        <v>818</v>
+      </c>
+      <c r="I31">
+        <v>1056</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
+        <v>0.6632365319865322</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32">
+        <v>200</v>
+      </c>
+      <c r="B32">
         <v>20</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
+      <c r="C32">
+        <v>60</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>60</v>
+      </c>
+      <c r="H32">
+        <v>1354</v>
+      </c>
+      <c r="I32">
+        <v>1357</v>
+      </c>
+      <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>0.589314664701551</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33">
+        <v>200</v>
+      </c>
+      <c r="B33">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>531</v>
-      </c>
-      <c r="G3">
-        <v>662</v>
-      </c>
-      <c r="H3">
-        <v>100</v>
-      </c>
-      <c r="I3">
-        <v>0.6682024169184283</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
+      <c r="C33">
+        <v>60</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>60</v>
+      </c>
+      <c r="H33">
+        <v>1297</v>
+      </c>
+      <c r="I33">
+        <v>1453</v>
+      </c>
+      <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
+        <v>0.5894815324615755</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34">
+        <v>200</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
+      </c>
+      <c r="C34">
+        <v>60</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>60</v>
+      </c>
+      <c r="H34">
+        <v>1237</v>
+      </c>
+      <c r="I34">
+        <v>1388</v>
+      </c>
+      <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>0.6062680115273802</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35">
+        <v>200</v>
+      </c>
+      <c r="B35">
+        <v>20</v>
+      </c>
+      <c r="C35">
+        <v>60</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>10</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35">
+        <v>60</v>
+      </c>
+      <c r="H35">
+        <v>1240</v>
+      </c>
+      <c r="I35">
+        <v>1451</v>
+      </c>
+      <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
+        <v>0.6058235699517589</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36">
+        <v>200</v>
+      </c>
+      <c r="B36">
+        <v>20</v>
+      </c>
+      <c r="C36">
+        <v>60</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>10</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>60</v>
+      </c>
+      <c r="H36">
+        <v>1284</v>
+      </c>
+      <c r="I36">
+        <v>1395</v>
+      </c>
+      <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
+        <v>0.5148148148148146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37">
+        <v>200</v>
+      </c>
+      <c r="B37">
+        <v>20</v>
+      </c>
+      <c r="C37">
+        <v>60</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37">
+        <v>60</v>
+      </c>
+      <c r="H37">
+        <v>1322</v>
+      </c>
+      <c r="I37">
+        <v>1362</v>
+      </c>
+      <c r="J37">
+        <v>100</v>
+      </c>
+      <c r="K37">
+        <v>0.6357317670093037</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38">
+        <v>200</v>
+      </c>
+      <c r="B38">
+        <v>20</v>
+      </c>
+      <c r="C38">
+        <v>60</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>60</v>
+      </c>
+      <c r="H38">
+        <v>1296</v>
+      </c>
+      <c r="I38">
+        <v>1491</v>
+      </c>
+      <c r="J38">
+        <v>100</v>
+      </c>
+      <c r="K38">
+        <v>0.6672814665772394</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39">
+        <v>200</v>
+      </c>
+      <c r="B39">
+        <v>20</v>
+      </c>
+      <c r="C39">
+        <v>60</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>60</v>
+      </c>
+      <c r="H39">
+        <v>1333</v>
+      </c>
+      <c r="I39">
+        <v>1464</v>
+      </c>
+      <c r="J39">
+        <v>100</v>
+      </c>
+      <c r="K39">
+        <v>0.6485997267759536</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40">
+        <v>200</v>
+      </c>
+      <c r="B40">
+        <v>20</v>
+      </c>
+      <c r="C40">
+        <v>60</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>10</v>
+      </c>
+      <c r="F40">
+        <v>9</v>
+      </c>
+      <c r="G40">
+        <v>60</v>
+      </c>
+      <c r="H40">
+        <v>1269</v>
+      </c>
+      <c r="I40">
+        <v>1460</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+      <c r="K40">
+        <v>0.6460045662100465</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41">
+        <v>200</v>
+      </c>
+      <c r="B41">
+        <v>20</v>
+      </c>
+      <c r="C41">
+        <v>60</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>60</v>
+      </c>
+      <c r="H41">
+        <v>1412</v>
+      </c>
+      <c r="I41">
+        <v>1470</v>
+      </c>
+      <c r="J41">
+        <v>100</v>
+      </c>
+      <c r="K41">
+        <v>0.6157482993197312</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42">
+        <v>250</v>
+      </c>
+      <c r="B42">
+        <v>25</v>
+      </c>
+      <c r="C42">
+        <v>75</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>10</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>75</v>
+      </c>
+      <c r="H42">
+        <v>1586</v>
+      </c>
+      <c r="I42">
+        <v>1869</v>
+      </c>
+      <c r="J42">
+        <v>100</v>
+      </c>
+      <c r="K42">
+        <v>0.6618441234171552</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43">
+        <v>250</v>
+      </c>
+      <c r="B43">
+        <v>25</v>
+      </c>
+      <c r="C43">
+        <v>75</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43">
+        <v>75</v>
+      </c>
+      <c r="H43">
+        <v>1567</v>
+      </c>
+      <c r="I43">
+        <v>1888</v>
+      </c>
+      <c r="J43">
+        <v>100</v>
+      </c>
+      <c r="K43">
+        <v>0.6450706214689237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44">
+        <v>250</v>
+      </c>
+      <c r="B44">
+        <v>25</v>
+      </c>
+      <c r="C44">
+        <v>75</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>10</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>75</v>
+      </c>
+      <c r="H44">
+        <v>1572</v>
+      </c>
+      <c r="I44">
+        <v>1807</v>
+      </c>
+      <c r="J44">
+        <v>100</v>
+      </c>
+      <c r="K44">
+        <v>0.6448994650433585</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45">
+        <v>250</v>
+      </c>
+      <c r="B45">
+        <v>25</v>
+      </c>
+      <c r="C45">
+        <v>75</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>10</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>75</v>
+      </c>
+      <c r="H45">
+        <v>1477</v>
+      </c>
+      <c r="I45">
+        <v>1811</v>
+      </c>
+      <c r="J45">
+        <v>100</v>
+      </c>
+      <c r="K45">
+        <v>0.62065157371618</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46">
+        <v>250</v>
+      </c>
+      <c r="B46">
+        <v>25</v>
+      </c>
+      <c r="C46">
+        <v>75</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46">
+        <v>75</v>
+      </c>
+      <c r="H46">
+        <v>1786</v>
+      </c>
+      <c r="I46">
+        <v>1958</v>
+      </c>
+      <c r="J46">
+        <v>100</v>
+      </c>
+      <c r="K46">
+        <v>0.589329247531499</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47">
+        <v>250</v>
+      </c>
+      <c r="B47">
+        <v>25</v>
+      </c>
+      <c r="C47">
+        <v>75</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>10</v>
+      </c>
+      <c r="F47">
+        <v>6</v>
+      </c>
+      <c r="G47">
+        <v>75</v>
+      </c>
+      <c r="H47">
+        <v>1649</v>
+      </c>
+      <c r="I47">
+        <v>1809</v>
+      </c>
+      <c r="J47">
+        <v>100</v>
+      </c>
+      <c r="K47">
+        <v>0.531534918002584</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48">
+        <v>250</v>
+      </c>
+      <c r="B48">
+        <v>25</v>
+      </c>
+      <c r="C48">
+        <v>75</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>10</v>
+      </c>
+      <c r="F48">
+        <v>7</v>
+      </c>
+      <c r="G48">
+        <v>75</v>
+      </c>
+      <c r="H48">
+        <v>1606</v>
+      </c>
+      <c r="I48">
+        <v>2027</v>
+      </c>
+      <c r="J48">
+        <v>100</v>
+      </c>
+      <c r="K48">
+        <v>0.6596743956586103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49">
+        <v>250</v>
+      </c>
+      <c r="B49">
+        <v>25</v>
+      </c>
+      <c r="C49">
+        <v>75</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="G49">
+        <v>75</v>
+      </c>
+      <c r="H49">
+        <v>1589</v>
+      </c>
+      <c r="I49">
+        <v>1906</v>
+      </c>
+      <c r="J49">
+        <v>100</v>
+      </c>
+      <c r="K49">
+        <v>0.6535921650926935</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50">
+        <v>250</v>
+      </c>
+      <c r="B50">
+        <v>25</v>
+      </c>
+      <c r="C50">
+        <v>75</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>10</v>
+      </c>
+      <c r="F50">
+        <v>9</v>
+      </c>
+      <c r="G50">
+        <v>75</v>
+      </c>
+      <c r="H50">
+        <v>1740</v>
+      </c>
+      <c r="I50">
+        <v>1825</v>
+      </c>
+      <c r="J50">
+        <v>100</v>
+      </c>
+      <c r="K50">
+        <v>0.6058447488584502</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51">
+        <v>250</v>
+      </c>
+      <c r="B51">
+        <v>25</v>
+      </c>
+      <c r="C51">
+        <v>75</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>10</v>
+      </c>
+      <c r="F51">
+        <v>10</v>
+      </c>
+      <c r="G51">
+        <v>75</v>
+      </c>
+      <c r="H51">
+        <v>1633</v>
+      </c>
+      <c r="I51">
+        <v>1898</v>
+      </c>
+      <c r="J51">
+        <v>100</v>
+      </c>
+      <c r="K51">
+        <v>0.6717175974710264</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52">
+        <v>300</v>
+      </c>
+      <c r="B52">
+        <v>30</v>
+      </c>
+      <c r="C52">
+        <v>90</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>10</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>90</v>
+      </c>
+      <c r="H52">
+        <v>2033</v>
+      </c>
+      <c r="I52">
+        <v>2083</v>
+      </c>
+      <c r="J52">
+        <v>100</v>
+      </c>
+      <c r="K52">
+        <v>0.5648477089667701</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53">
+        <v>300</v>
+      </c>
+      <c r="B53">
+        <v>30</v>
+      </c>
+      <c r="C53">
+        <v>90</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>10</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="G53">
+        <v>90</v>
+      </c>
+      <c r="H53">
+        <v>2225</v>
+      </c>
+      <c r="I53">
+        <v>2287</v>
+      </c>
+      <c r="J53">
+        <v>100</v>
+      </c>
+      <c r="K53">
+        <v>0.6185638633824093</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54">
+        <v>300</v>
+      </c>
+      <c r="B54">
+        <v>30</v>
+      </c>
+      <c r="C54">
+        <v>90</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>10</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <v>90</v>
+      </c>
+      <c r="H54">
+        <v>2212</v>
+      </c>
+      <c r="I54">
+        <v>2337</v>
+      </c>
+      <c r="J54">
+        <v>100</v>
+      </c>
+      <c r="K54">
+        <v>0.6264726857794846</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55">
+        <v>300</v>
+      </c>
+      <c r="B55">
+        <v>30</v>
+      </c>
+      <c r="C55">
+        <v>90</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>10</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+      <c r="G55">
+        <v>90</v>
+      </c>
+      <c r="H55">
+        <v>1867</v>
+      </c>
+      <c r="I55">
+        <v>2247</v>
+      </c>
+      <c r="J55">
+        <v>100</v>
+      </c>
+      <c r="K55">
+        <v>0.6553478712357191</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56">
+        <v>300</v>
+      </c>
+      <c r="B56">
+        <v>30</v>
+      </c>
+      <c r="C56">
+        <v>90</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>90</v>
+      </c>
+      <c r="H56">
+        <v>1841</v>
+      </c>
+      <c r="I56">
+        <v>2136</v>
+      </c>
+      <c r="J56">
+        <v>100</v>
+      </c>
+      <c r="K56">
+        <v>0.5687682064086551</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57">
+        <v>300</v>
+      </c>
+      <c r="B57">
+        <v>30</v>
+      </c>
+      <c r="C57">
+        <v>90</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>10</v>
+      </c>
+      <c r="F57">
+        <v>6</v>
+      </c>
+      <c r="G57">
+        <v>90</v>
+      </c>
+      <c r="H57">
+        <v>2062</v>
+      </c>
+      <c r="I57">
+        <v>2121</v>
+      </c>
+      <c r="J57">
+        <v>100</v>
+      </c>
+      <c r="K57">
+        <v>0.5848761066582807</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>300</v>
+      </c>
+      <c r="B58">
+        <v>30</v>
+      </c>
+      <c r="C58">
+        <v>90</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="F58">
+        <v>7</v>
+      </c>
+      <c r="G58">
+        <v>90</v>
+      </c>
+      <c r="H58">
+        <v>1969</v>
+      </c>
+      <c r="I58">
+        <v>2133</v>
+      </c>
+      <c r="J58">
+        <v>100</v>
+      </c>
+      <c r="K58">
+        <v>0.6225243527634481</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>300</v>
+      </c>
+      <c r="B59">
+        <v>30</v>
+      </c>
+      <c r="C59">
+        <v>90</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>10</v>
+      </c>
+      <c r="F59">
+        <v>8</v>
+      </c>
+      <c r="G59">
+        <v>90</v>
+      </c>
+      <c r="H59">
+        <v>2185</v>
+      </c>
+      <c r="I59">
+        <v>2287</v>
+      </c>
+      <c r="J59">
+        <v>100</v>
+      </c>
+      <c r="K59">
+        <v>0.5870281300101988</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>300</v>
+      </c>
+      <c r="B60">
+        <v>30</v>
+      </c>
+      <c r="C60">
+        <v>90</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>10</v>
+      </c>
+      <c r="F60">
+        <v>9</v>
+      </c>
+      <c r="G60">
+        <v>90</v>
+      </c>
+      <c r="H60">
+        <v>1921</v>
+      </c>
+      <c r="I60">
+        <v>2162</v>
+      </c>
+      <c r="J60">
+        <v>100</v>
+      </c>
+      <c r="K60">
+        <v>0.6643437146674879</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>300</v>
+      </c>
+      <c r="B61">
+        <v>30</v>
+      </c>
+      <c r="C61">
+        <v>90</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>10</v>
+      </c>
+      <c r="F61">
+        <v>10</v>
+      </c>
+      <c r="G61">
+        <v>90</v>
+      </c>
+      <c r="H61">
+        <v>1859</v>
+      </c>
+      <c r="I61">
+        <v>2045</v>
+      </c>
+      <c r="J61">
+        <v>100</v>
+      </c>
+      <c r="K61">
+        <v>0.5640369464819344</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>350</v>
+      </c>
+      <c r="B62">
+        <v>35</v>
+      </c>
+      <c r="C62">
+        <v>105</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>10</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>105</v>
+      </c>
+      <c r="H62">
+        <v>2069</v>
+      </c>
+      <c r="I62">
+        <v>2529</v>
+      </c>
+      <c r="J62">
+        <v>100</v>
+      </c>
+      <c r="K62">
+        <v>0.5759400478261704</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>350</v>
+      </c>
+      <c r="B63">
+        <v>35</v>
+      </c>
+      <c r="C63">
+        <v>105</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>10</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>105</v>
+      </c>
+      <c r="H63">
+        <v>2124</v>
+      </c>
+      <c r="I63">
+        <v>2330</v>
+      </c>
+      <c r="J63">
+        <v>100</v>
+      </c>
+      <c r="K63">
+        <v>0.6133946454118154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>350</v>
+      </c>
+      <c r="B64">
+        <v>35</v>
+      </c>
+      <c r="C64">
+        <v>105</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>10</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <v>105</v>
+      </c>
+      <c r="H64">
+        <v>2391</v>
+      </c>
+      <c r="I64">
+        <v>2470</v>
+      </c>
+      <c r="J64">
+        <v>100</v>
+      </c>
+      <c r="K64">
+        <v>0.5966724503566595</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65">
+        <v>350</v>
+      </c>
+      <c r="B65">
+        <v>35</v>
+      </c>
+      <c r="C65">
+        <v>105</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>10</v>
+      </c>
+      <c r="F65">
+        <v>4</v>
+      </c>
+      <c r="G65">
+        <v>105</v>
+      </c>
+      <c r="H65">
+        <v>2253</v>
+      </c>
+      <c r="I65">
+        <v>2452</v>
+      </c>
+      <c r="J65">
+        <v>100</v>
+      </c>
+      <c r="K65">
+        <v>0.539979025868094</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>350</v>
+      </c>
+      <c r="B66">
+        <v>35</v>
+      </c>
+      <c r="C66">
+        <v>105</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>10</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>105</v>
+      </c>
+      <c r="H66">
+        <v>2225</v>
+      </c>
+      <c r="I66">
+        <v>2522</v>
+      </c>
+      <c r="J66">
+        <v>100</v>
+      </c>
+      <c r="K66">
+        <v>0.6199388240625361</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>350</v>
+      </c>
+      <c r="B67">
+        <v>35</v>
+      </c>
+      <c r="C67">
+        <v>105</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>10</v>
+      </c>
+      <c r="F67">
+        <v>6</v>
+      </c>
+      <c r="G67">
+        <v>105</v>
+      </c>
+      <c r="H67">
+        <v>2504</v>
+      </c>
+      <c r="I67">
+        <v>2540</v>
+      </c>
+      <c r="J67">
+        <v>100</v>
+      </c>
+      <c r="K67">
+        <v>0.6382977127858945</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>350</v>
+      </c>
+      <c r="B68">
+        <v>35</v>
+      </c>
+      <c r="C68">
+        <v>105</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>10</v>
+      </c>
+      <c r="F68">
+        <v>7</v>
+      </c>
+      <c r="G68">
+        <v>105</v>
+      </c>
+      <c r="H68">
+        <v>2354</v>
+      </c>
+      <c r="I68">
+        <v>2567</v>
+      </c>
+      <c r="J68">
+        <v>100</v>
+      </c>
+      <c r="K68">
+        <v>0.632107147494756</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69">
+        <v>350</v>
+      </c>
+      <c r="B69">
+        <v>35</v>
+      </c>
+      <c r="C69">
+        <v>105</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>10</v>
+      </c>
+      <c r="F69">
+        <v>8</v>
+      </c>
+      <c r="G69">
+        <v>105</v>
+      </c>
+      <c r="H69">
+        <v>2266</v>
+      </c>
+      <c r="I69">
+        <v>2415</v>
+      </c>
+      <c r="J69">
+        <v>100</v>
+      </c>
+      <c r="K69">
+        <v>0.5658680863649821</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70">
+        <v>350</v>
+      </c>
+      <c r="B70">
+        <v>35</v>
+      </c>
+      <c r="C70">
+        <v>105</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>10</v>
+      </c>
+      <c r="F70">
+        <v>9</v>
+      </c>
+      <c r="G70">
+        <v>105</v>
+      </c>
+      <c r="H70">
+        <v>2396</v>
+      </c>
+      <c r="I70">
+        <v>2567</v>
+      </c>
+      <c r="J70">
+        <v>100</v>
+      </c>
+      <c r="K70">
+        <v>0.6165358858775267</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71">
+        <v>350</v>
+      </c>
+      <c r="B71">
+        <v>35</v>
+      </c>
+      <c r="C71">
+        <v>105</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>10</v>
+      </c>
+      <c r="F71">
+        <v>10</v>
+      </c>
+      <c r="G71">
+        <v>105</v>
+      </c>
+      <c r="H71">
+        <v>2225</v>
+      </c>
+      <c r="I71">
+        <v>2544</v>
+      </c>
+      <c r="J71">
+        <v>100</v>
+      </c>
+      <c r="K71">
+        <v>0.631622491764</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72">
+        <v>400</v>
+      </c>
+      <c r="B72">
+        <v>40</v>
+      </c>
+      <c r="C72">
+        <v>120</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>10</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>120</v>
+      </c>
+      <c r="H72">
+        <v>2717</v>
+      </c>
+      <c r="I72">
+        <v>2955</v>
+      </c>
+      <c r="J72">
+        <v>100</v>
+      </c>
+      <c r="K72">
+        <v>0.5977270163564582</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73">
+        <v>400</v>
+      </c>
+      <c r="B73">
+        <v>40</v>
+      </c>
+      <c r="C73">
+        <v>120</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>10</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>120</v>
+      </c>
+      <c r="H73">
+        <v>2480</v>
+      </c>
+      <c r="I73">
+        <v>2742</v>
+      </c>
+      <c r="J73">
+        <v>100</v>
+      </c>
+      <c r="K73">
+        <v>0.5551027230731759</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74">
+        <v>400</v>
+      </c>
+      <c r="B74">
+        <v>40</v>
+      </c>
+      <c r="C74">
+        <v>120</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>10</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74">
+        <v>120</v>
+      </c>
+      <c r="H74">
+        <v>2923</v>
+      </c>
+      <c r="I74">
+        <v>3213</v>
+      </c>
+      <c r="J74">
+        <v>100</v>
+      </c>
+      <c r="K74">
+        <v>0.6437467579624252</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>400</v>
+      </c>
+      <c r="B75">
+        <v>40</v>
+      </c>
+      <c r="C75">
+        <v>120</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>10</v>
+      </c>
+      <c r="F75">
+        <v>4</v>
+      </c>
+      <c r="G75">
+        <v>120</v>
+      </c>
+      <c r="H75">
+        <v>2494</v>
+      </c>
+      <c r="I75">
+        <v>2767</v>
+      </c>
+      <c r="J75">
+        <v>100</v>
+      </c>
+      <c r="K75">
+        <v>0.5703589928924173</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76">
+        <v>400</v>
+      </c>
+      <c r="B76">
+        <v>40</v>
+      </c>
+      <c r="C76">
+        <v>120</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>10</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>120</v>
+      </c>
+      <c r="H76">
+        <v>2715</v>
+      </c>
+      <c r="I76">
+        <v>3045</v>
+      </c>
+      <c r="J76">
+        <v>100</v>
+      </c>
+      <c r="K76">
+        <v>0.6276792556102921</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77">
+        <v>400</v>
+      </c>
+      <c r="B77">
+        <v>40</v>
+      </c>
+      <c r="C77">
+        <v>120</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+      <c r="F77">
+        <v>6</v>
+      </c>
+      <c r="G77">
+        <v>120</v>
+      </c>
+      <c r="H77">
+        <v>2583</v>
+      </c>
+      <c r="I77">
+        <v>3222</v>
+      </c>
+      <c r="J77">
+        <v>100</v>
+      </c>
+      <c r="K77">
+        <v>0.6649622387750831</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78">
+        <v>400</v>
+      </c>
+      <c r="B78">
+        <v>40</v>
+      </c>
+      <c r="C78">
+        <v>120</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>10</v>
+      </c>
+      <c r="F78">
+        <v>7</v>
+      </c>
+      <c r="G78">
+        <v>120</v>
+      </c>
+      <c r="H78">
+        <v>2644</v>
+      </c>
+      <c r="I78">
+        <v>2757</v>
+      </c>
+      <c r="J78">
+        <v>100</v>
+      </c>
+      <c r="K78">
+        <v>0.5766140732680413</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79">
+        <v>400</v>
+      </c>
+      <c r="B79">
+        <v>40</v>
+      </c>
+      <c r="C79">
+        <v>120</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>10</v>
+      </c>
+      <c r="F79">
+        <v>8</v>
+      </c>
+      <c r="G79">
+        <v>120</v>
+      </c>
+      <c r="H79">
+        <v>3045</v>
+      </c>
+      <c r="I79">
+        <v>3069</v>
+      </c>
+      <c r="J79">
+        <v>100</v>
+      </c>
+      <c r="K79">
+        <v>0.6128787878787654</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80">
+        <v>400</v>
+      </c>
+      <c r="B80">
+        <v>40</v>
+      </c>
+      <c r="C80">
+        <v>120</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>10</v>
+      </c>
+      <c r="F80">
+        <v>9</v>
+      </c>
+      <c r="G80">
+        <v>120</v>
+      </c>
+      <c r="H80">
+        <v>2881</v>
+      </c>
+      <c r="I80">
+        <v>3150</v>
+      </c>
+      <c r="J80">
+        <v>100</v>
+      </c>
+      <c r="K80">
+        <v>0.6336878306878166</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81">
+        <v>400</v>
+      </c>
+      <c r="B81">
+        <v>40</v>
+      </c>
+      <c r="C81">
+        <v>120</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>10</v>
+      </c>
+      <c r="F81">
+        <v>10</v>
+      </c>
+      <c r="G81">
+        <v>120</v>
+      </c>
+      <c r="H81">
+        <v>2848</v>
+      </c>
+      <c r="I81">
+        <v>2930</v>
+      </c>
+      <c r="J81">
+        <v>100</v>
+      </c>
+      <c r="K81">
+        <v>0.6186205915813364</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82">
+        <v>450</v>
+      </c>
+      <c r="B82">
+        <v>45</v>
+      </c>
+      <c r="C82">
+        <v>135</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>10</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>135</v>
+      </c>
+      <c r="H82">
+        <v>2899</v>
+      </c>
+      <c r="I82">
+        <v>3098</v>
+      </c>
+      <c r="J82">
+        <v>100</v>
+      </c>
+      <c r="K82">
+        <v>0.5929225545752337</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83">
+        <v>450</v>
+      </c>
+      <c r="B83">
+        <v>45</v>
+      </c>
+      <c r="C83">
+        <v>135</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>10</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>135</v>
+      </c>
+      <c r="H83">
+        <v>2964</v>
+      </c>
+      <c r="I83">
+        <v>3203</v>
+      </c>
+      <c r="J83">
+        <v>100</v>
+      </c>
+      <c r="K83">
+        <v>0.6525548964512541</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84">
+        <v>450</v>
+      </c>
+      <c r="B84">
+        <v>45</v>
+      </c>
+      <c r="C84">
+        <v>135</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>10</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="G84">
+        <v>135</v>
+      </c>
+      <c r="H84">
+        <v>2870</v>
+      </c>
+      <c r="I84">
+        <v>3021</v>
+      </c>
+      <c r="J84">
+        <v>100</v>
+      </c>
+      <c r="K84">
+        <v>0.569367513822994</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85">
+        <v>450</v>
+      </c>
+      <c r="B85">
+        <v>45</v>
+      </c>
+      <c r="C85">
+        <v>135</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>10</v>
+      </c>
+      <c r="F85">
+        <v>4</v>
+      </c>
+      <c r="G85">
+        <v>135</v>
+      </c>
+      <c r="H85">
+        <v>2998</v>
+      </c>
+      <c r="I85">
+        <v>3144</v>
+      </c>
+      <c r="J85">
+        <v>100</v>
+      </c>
+      <c r="K85">
+        <v>0.5724790311940471</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86">
+        <v>450</v>
+      </c>
+      <c r="B86">
+        <v>45</v>
+      </c>
+      <c r="C86">
+        <v>135</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>10</v>
+      </c>
+      <c r="F86">
+        <v>5</v>
+      </c>
+      <c r="G86">
+        <v>135</v>
+      </c>
+      <c r="H86">
+        <v>3185</v>
+      </c>
+      <c r="I86">
+        <v>3694</v>
+      </c>
+      <c r="J86">
+        <v>100</v>
+      </c>
+      <c r="K86">
+        <v>0.657079548416865</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87">
+        <v>450</v>
+      </c>
+      <c r="B87">
+        <v>45</v>
+      </c>
+      <c r="C87">
+        <v>135</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>10</v>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87">
+        <v>135</v>
+      </c>
+      <c r="H87">
+        <v>3103</v>
+      </c>
+      <c r="I87">
+        <v>3347</v>
+      </c>
+      <c r="J87">
+        <v>100</v>
+      </c>
+      <c r="K87">
+        <v>0.6100786774225777</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88">
+        <v>450</v>
+      </c>
+      <c r="B88">
+        <v>45</v>
+      </c>
+      <c r="C88">
+        <v>135</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>10</v>
+      </c>
+      <c r="F88">
+        <v>7</v>
+      </c>
+      <c r="G88">
+        <v>135</v>
+      </c>
+      <c r="H88">
+        <v>2787</v>
+      </c>
+      <c r="I88">
+        <v>3151</v>
+      </c>
+      <c r="J88">
+        <v>100</v>
+      </c>
+      <c r="K88">
+        <v>0.6004795655700133</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89">
+        <v>450</v>
+      </c>
+      <c r="B89">
+        <v>45</v>
+      </c>
+      <c r="C89">
+        <v>135</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>10</v>
+      </c>
+      <c r="F89">
+        <v>8</v>
+      </c>
+      <c r="G89">
+        <v>135</v>
+      </c>
+      <c r="H89">
+        <v>3068</v>
+      </c>
+      <c r="I89">
+        <v>3277</v>
+      </c>
+      <c r="J89">
+        <v>100</v>
+      </c>
+      <c r="K89">
+        <v>0.6430135964466185</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90">
+        <v>450</v>
+      </c>
+      <c r="B90">
+        <v>45</v>
+      </c>
+      <c r="C90">
+        <v>135</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>10</v>
+      </c>
+      <c r="F90">
+        <v>9</v>
+      </c>
+      <c r="G90">
+        <v>135</v>
+      </c>
+      <c r="H90">
+        <v>2991</v>
+      </c>
+      <c r="I90">
+        <v>3099</v>
+      </c>
+      <c r="J90">
+        <v>100</v>
+      </c>
+      <c r="K90">
+        <v>0.604668172528779</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91">
+        <v>450</v>
+      </c>
+      <c r="B91">
+        <v>45</v>
+      </c>
+      <c r="C91">
+        <v>135</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>10</v>
+      </c>
+      <c r="F91">
+        <v>10</v>
+      </c>
+      <c r="G91">
+        <v>135</v>
+      </c>
+      <c r="H91">
+        <v>2749</v>
+      </c>
+      <c r="I91">
+        <v>3241</v>
+      </c>
+      <c r="J91">
+        <v>100</v>
+      </c>
+      <c r="K91">
+        <v>0.6242152056406911</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92">
+        <v>500</v>
+      </c>
+      <c r="B92">
+        <v>50</v>
+      </c>
+      <c r="C92">
         <v>150</v>
       </c>
-      <c r="B4">
-        <v>15</v>
-      </c>
-      <c r="C4">
-        <v>30</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>901</v>
-      </c>
-      <c r="G4">
-        <v>1117</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
-      <c r="I4">
-        <v>0.647120262608175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
-        <v>200</v>
-      </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>40</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>40</v>
-      </c>
-      <c r="F5">
-        <v>1360</v>
-      </c>
-      <c r="G5">
-        <v>1497</v>
-      </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
-      <c r="I5">
-        <v>0.6321309285237133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6">
-        <v>250</v>
-      </c>
-      <c r="B6">
-        <v>25</v>
-      </c>
-      <c r="C6">
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>10</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>150</v>
+      </c>
+      <c r="H92">
+        <v>3186</v>
+      </c>
+      <c r="I92">
+        <v>3736</v>
+      </c>
+      <c r="J92">
+        <v>100</v>
+      </c>
+      <c r="K92">
+        <v>0.5777480371163485</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93">
+        <v>500</v>
+      </c>
+      <c r="B93">
         <v>50</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
+      <c r="C93">
+        <v>150</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>10</v>
+      </c>
+      <c r="F93">
+        <v>2</v>
+      </c>
+      <c r="G93">
+        <v>150</v>
+      </c>
+      <c r="H93">
+        <v>3490</v>
+      </c>
+      <c r="I93">
+        <v>3758</v>
+      </c>
+      <c r="J93">
+        <v>100</v>
+      </c>
+      <c r="K93">
+        <v>0.6341014724144163</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94">
+        <v>500</v>
+      </c>
+      <c r="B94">
         <v>50</v>
       </c>
-      <c r="F6">
-        <v>1527</v>
-      </c>
-      <c r="G6">
-        <v>1812</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
-      <c r="I6">
-        <v>0.6334988962472375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7">
-        <v>300</v>
-      </c>
-      <c r="B7">
-        <v>30</v>
-      </c>
-      <c r="C7">
-        <v>60</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>60</v>
-      </c>
-      <c r="F7">
-        <v>1963</v>
-      </c>
-      <c r="G7">
-        <v>2173</v>
-      </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
-      <c r="I7">
-        <v>0.6161834637214313</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8">
-        <v>350</v>
-      </c>
-      <c r="B8">
-        <v>35</v>
-      </c>
-      <c r="C8">
-        <v>70</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>70</v>
-      </c>
-      <c r="F8">
-        <v>2150</v>
-      </c>
-      <c r="G8">
-        <v>2595</v>
-      </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
-      <c r="I8">
-        <v>0.6505092210294505</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9">
-        <v>400</v>
-      </c>
-      <c r="B9">
-        <v>40</v>
-      </c>
-      <c r="C9">
-        <v>80</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>80</v>
-      </c>
-      <c r="F9">
-        <v>2333</v>
-      </c>
-      <c r="G9">
-        <v>2717</v>
-      </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
-      <c r="I9">
-        <v>0.5990798675009156</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10">
-        <v>450</v>
-      </c>
-      <c r="B10">
-        <v>45</v>
-      </c>
-      <c r="C10">
-        <v>90</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>90</v>
-      </c>
-      <c r="F10">
-        <v>2883</v>
-      </c>
-      <c r="G10">
-        <v>3207</v>
-      </c>
-      <c r="H10">
-        <v>100</v>
-      </c>
-      <c r="I10">
-        <v>0.604448602016421</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11">
+      <c r="C94">
+        <v>150</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>10</v>
+      </c>
+      <c r="F94">
+        <v>3</v>
+      </c>
+      <c r="G94">
+        <v>150</v>
+      </c>
+      <c r="H94">
+        <v>3535</v>
+      </c>
+      <c r="I94">
+        <v>3816</v>
+      </c>
+      <c r="J94">
+        <v>100</v>
+      </c>
+      <c r="K94">
+        <v>0.6191736547868706</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95">
         <v>500</v>
       </c>
-      <c r="B11">
+      <c r="B95">
         <v>50</v>
       </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11">
-        <v>3535</v>
-      </c>
-      <c r="G11">
-        <v>3742</v>
-      </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
-      <c r="I11">
-        <v>0.6287733832175264</v>
+      <c r="C95">
+        <v>150</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>10</v>
+      </c>
+      <c r="F95">
+        <v>4</v>
+      </c>
+      <c r="G95">
+        <v>150</v>
+      </c>
+      <c r="H95">
+        <v>3323</v>
+      </c>
+      <c r="I95">
+        <v>3879</v>
+      </c>
+      <c r="J95">
+        <v>100</v>
+      </c>
+      <c r="K95">
+        <v>0.6491088768583005</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96">
+        <v>500</v>
+      </c>
+      <c r="B96">
+        <v>50</v>
+      </c>
+      <c r="C96">
+        <v>150</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>10</v>
+      </c>
+      <c r="F96">
+        <v>5</v>
+      </c>
+      <c r="G96">
+        <v>150</v>
+      </c>
+      <c r="H96">
+        <v>3605</v>
+      </c>
+      <c r="I96">
+        <v>3918</v>
+      </c>
+      <c r="J96">
+        <v>100</v>
+      </c>
+      <c r="K96">
+        <v>0.6364726901480384</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97">
+        <v>500</v>
+      </c>
+      <c r="B97">
+        <v>50</v>
+      </c>
+      <c r="C97">
+        <v>150</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>10</v>
+      </c>
+      <c r="F97">
+        <v>6</v>
+      </c>
+      <c r="G97">
+        <v>150</v>
+      </c>
+      <c r="H97">
+        <v>3901</v>
+      </c>
+      <c r="I97">
+        <v>4101</v>
+      </c>
+      <c r="J97">
+        <v>100</v>
+      </c>
+      <c r="K97">
+        <v>0.6663870600666527</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98">
+        <v>500</v>
+      </c>
+      <c r="B98">
+        <v>50</v>
+      </c>
+      <c r="C98">
+        <v>150</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>10</v>
+      </c>
+      <c r="F98">
+        <v>7</v>
+      </c>
+      <c r="G98">
+        <v>150</v>
+      </c>
+      <c r="H98">
+        <v>3335</v>
+      </c>
+      <c r="I98">
+        <v>3656</v>
+      </c>
+      <c r="J98">
+        <v>100</v>
+      </c>
+      <c r="K98">
+        <v>0.6185302698760073</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99">
+        <v>500</v>
+      </c>
+      <c r="B99">
+        <v>50</v>
+      </c>
+      <c r="C99">
+        <v>150</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>10</v>
+      </c>
+      <c r="F99">
+        <v>8</v>
+      </c>
+      <c r="G99">
+        <v>150</v>
+      </c>
+      <c r="H99">
+        <v>3117</v>
+      </c>
+      <c r="I99">
+        <v>3735</v>
+      </c>
+      <c r="J99">
+        <v>100</v>
+      </c>
+      <c r="K99">
+        <v>0.6614404283801892</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100">
+        <v>500</v>
+      </c>
+      <c r="B100">
+        <v>50</v>
+      </c>
+      <c r="C100">
+        <v>150</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>10</v>
+      </c>
+      <c r="F100">
+        <v>9</v>
+      </c>
+      <c r="G100">
+        <v>150</v>
+      </c>
+      <c r="H100">
+        <v>3263</v>
+      </c>
+      <c r="I100">
+        <v>3599</v>
+      </c>
+      <c r="J100">
+        <v>100</v>
+      </c>
+      <c r="K100">
+        <v>0.6217949430397411</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101">
+        <v>500</v>
+      </c>
+      <c r="B101">
+        <v>50</v>
+      </c>
+      <c r="C101">
+        <v>150</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>10</v>
+      </c>
+      <c r="F101">
+        <v>10</v>
+      </c>
+      <c r="G101">
+        <v>150</v>
+      </c>
+      <c r="H101">
+        <v>3378</v>
+      </c>
+      <c r="I101">
+        <v>3642</v>
+      </c>
+      <c r="J101">
+        <v>100</v>
+      </c>
+      <c r="K101">
+        <v>0.6540362438220789</v>
       </c>
     </row>
   </sheetData>
@@ -762,8 +3960,7 @@
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="21.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" customWidth="1"/>
@@ -772,32 +3969,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="F1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="G1" t="s">
         <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -811,22 +4008,22 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>241</v>
+        <v>314.4</v>
       </c>
       <c r="G2">
-        <v>380</v>
+        <v>347.5</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
       <c r="I2">
-        <v>0.6655263157894744</v>
+        <v>0.54941050048902</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -840,22 +4037,22 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>531</v>
+        <v>627.9</v>
       </c>
       <c r="G3">
-        <v>662</v>
+        <v>685.4</v>
       </c>
       <c r="H3">
         <v>100</v>
       </c>
       <c r="I3">
-        <v>0.6682024169184283</v>
+        <v>0.5643319617363126</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -869,22 +4066,22 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F4">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="G4">
-        <v>1117</v>
+        <v>1074.7</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0.647120262608175</v>
+        <v>0.6373786074816545</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -898,22 +4095,22 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F5">
-        <v>1360</v>
+        <v>1304.4</v>
       </c>
       <c r="G5">
-        <v>1497</v>
+        <v>1429.1</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0.6321309285237133</v>
+        <v>0.6119068419349355</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -927,22 +4124,22 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F6">
-        <v>1527</v>
+        <v>1620.5</v>
       </c>
       <c r="G6">
-        <v>1812</v>
+        <v>1879.8</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0.6334988962472375</v>
+        <v>0.6284158856260481</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -956,22 +4153,22 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E7">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F7">
-        <v>1963</v>
+        <v>2017.4</v>
       </c>
       <c r="G7">
-        <v>2173</v>
+        <v>2183.8</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0.6161834637214313</v>
+        <v>0.6056809586354388</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -985,22 +4182,22 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F8">
-        <v>2150</v>
+        <v>2280.7</v>
       </c>
       <c r="G8">
-        <v>2595</v>
+        <v>2493.6</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0.6505092210294505</v>
+        <v>0.6030356317812434</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1014,22 +4211,22 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F9">
-        <v>2333</v>
+        <v>2733</v>
       </c>
       <c r="G9">
-        <v>2717</v>
+        <v>2985</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0.5990798675009156</v>
+        <v>0.6101378268085812</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1043,22 +4240,22 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="F10">
-        <v>2883</v>
+        <v>2961.4</v>
       </c>
       <c r="G10">
-        <v>3207</v>
+        <v>3227.5</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0.604448602016421</v>
+        <v>0.6126858762069073</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1072,22 +4269,22 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F11">
-        <v>3535</v>
+        <v>3413.3</v>
       </c>
       <c r="G11">
-        <v>3742</v>
+        <v>3784</v>
       </c>
       <c r="H11">
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0.6287733832175264</v>
+        <v>0.6338793676508644</v>
       </c>
     </row>
   </sheetData>
